--- a/Checklists/source_code_review_checklist.xlsx
+++ b/Checklists/source_code_review_checklist.xlsx
@@ -27,9 +27,6 @@
     <t>Each line of code should have comment for better clarity.</t>
   </si>
   <si>
-    <t>In source code each if-block should have else block and each switch case should have default block.</t>
-  </si>
-  <si>
     <t>Each source file shouldn’t contain lines of code more than 3k.</t>
   </si>
   <si>
@@ -61,6 +58,9 @@
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>In source code each if block should have else block and each switch case should have default block.</t>
   </si>
 </sst>
 </file>
@@ -440,7 +440,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D1" s="5"/>
     </row>
@@ -449,7 +449,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -469,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -479,7 +479,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -489,7 +489,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -499,7 +499,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -509,7 +509,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -519,7 +519,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -529,24 +529,24 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
     <row r="3056" spans="6:6">
       <c r="F3056" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3057" spans="6:6">
       <c r="F3057" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3058" spans="6:6">
       <c r="F3058" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
